--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This extension specifies a list of periods of time (recurrent or not). It specifies the type of Schedule (busy-unavailable|free), the identifier of the period, the period with a possibly recurrence rule, the date of creation of the period and the priority of this period | Cette extension permet de préciser une liste de période de temps (récurrentes ou non). Elle spécifie le type de Schedule (busy-unavailable|free), l'identifiant de la période, la période (récurrente ou non avec une règle de récurrence dans le cas d'une période récurrente, la date de création de la période et une priorité.</t>
+    <t>Cette extension permet de préciser une liste de période de temps (récurrentes ou non). Elle spécifie le type de Schedule, l'identifiant de la période, la période (récurrente ou non avec une règle de récurrence dans le cas d'une période récurrente, la date de création de la période et une priorité.
++This extension specifies a list of periods of time (recurrent or not). It specifies the type of Schedule, the identifier of the period, the period with a possibly recurrence rule, the date of creation of the period and the priority of this period</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3411,10 +3411,10 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S20" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3870" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3869" uniqueCount="333">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -989,6 +989,9 @@
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-schedule-unavailability-reason</t>
   </si>
   <si>
     <t>Extension.extension:created</t>
@@ -1376,7 +1379,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.9921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -12361,13 +12364,11 @@
         <v>77</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>77</v>
+        <v>318</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>77</v>
@@ -12405,13 +12406,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>77</v>
@@ -12436,10 +12437,10 @@
         <v>92</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12510,7 +12511,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>101</v>
@@ -12613,7 +12614,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>103</v>
@@ -12716,7 +12717,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>105</v>
@@ -12759,7 +12760,7 @@
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>77</v>
@@ -12821,7 +12822,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>113</v>
@@ -12924,13 +12925,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>77</v>
@@ -13029,7 +13030,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>101</v>
@@ -13132,7 +13133,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>103</v>
@@ -13235,7 +13236,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>105</v>
@@ -13278,7 +13279,7 @@
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>77</v>
@@ -13340,7 +13341,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>113</v>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
